--- a/dcf/MELI.xlsx
+++ b/dcf/MELI.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1136,25 +1136,25 @@
         <v>11</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2975.730911053825</v>
+        <v>2838.447742119741</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2876.138157085074</v>
+        <v>2744.389198694377</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>2780.970997375047</v>
+        <v>2654.503975381573</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>2690.009450600186</v>
+        <v>2568.584771553364</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>2603.045492015466</v>
+        <v>2486.435549932728</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>2519.882351413768</v>
+        <v>2407.870875392095</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>2440.333855258251</v>
+        <v>2332.715295349911</v>
       </c>
     </row>
     <row r="6">
@@ -1162,25 +1162,25 @@
         <v>12</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>3132.623405548336</v>
+        <v>2986.142257319019</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3026.225628065776</v>
+        <v>2885.677641684593</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2924.576713855417</v>
+        <v>2789.690663207198</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2827.440001074456</v>
+        <v>2697.958318651739</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2734.591712885594</v>
+        <v>2610.269742131071</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>2645.820200003714</v>
+        <v>2526.425491740444</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2560.925230943984</v>
+        <v>2446.236881111565</v>
       </c>
     </row>
     <row r="7">
@@ -1188,25 +1188,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3289.515900042847</v>
+        <v>3133.836772518296</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>3176.313099046479</v>
+        <v>3026.966084674808</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>3068.182430335788</v>
+        <v>2924.877351032824</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2964.870551548726</v>
+        <v>2827.331865750113</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>2866.137933755722</v>
+        <v>2734.103934329413</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2771.75804859366</v>
+        <v>2644.980108088792</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2681.516606629719</v>
+        <v>2559.758466873218</v>
       </c>
     </row>
     <row r="8">
@@ -1214,25 +1214,25 @@
         <v>14</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3446.408394537358</v>
+        <v>3281.531287717573</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>3326.400570027182</v>
+        <v>3168.254527665024</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3211.788146816158</v>
+        <v>3060.064038858449</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>3102.301102022996</v>
+        <v>2956.705412848488</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2997.68415462585</v>
+        <v>2857.938126527756</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>2897.695897183607</v>
+        <v>2763.534724437141</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2802.107982315453</v>
+        <v>2673.280052634872</v>
       </c>
     </row>
     <row r="9">
@@ -1240,25 +1240,25 @@
         <v>15</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>3603.300889031868</v>
+        <v>3429.22580291685</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>3476.488041007884</v>
+        <v>3309.54297065524</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>3355.393863296526</v>
+        <v>3195.250726684074</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3239.731652497265</v>
+        <v>3086.078959946863</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>3129.230375495978</v>
+        <v>2981.772318726098</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>3023.633745773553</v>
+        <v>2882.089340785488</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2922.699358001187</v>
+        <v>2786.801638396526</v>
       </c>
     </row>
     <row r="10">
@@ -1266,25 +1266,25 @@
         <v>16</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>3760.193383526379</v>
+        <v>3576.920318116127</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3626.575511988587</v>
+        <v>3450.831413645456</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>3498.999579776896</v>
+        <v>3330.437414509699</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>3377.162202971535</v>
+        <v>3215.452507045237</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>3260.776596366108</v>
+        <v>3105.60651092444</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3149.571594363499</v>
+        <v>3000.643957133837</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>3043.29073368692</v>
+        <v>2900.323224158179</v>
       </c>
     </row>
     <row r="11">
@@ -1292,25 +1292,25 @@
         <v>17</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>3917.08587802089</v>
+        <v>3724.614833315404</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3776.66298296929</v>
+        <v>3592.119856635672</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3642.605296257266</v>
+        <v>3465.624102335325</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>3514.592753445806</v>
+        <v>3344.826054143612</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3392.322817236236</v>
+        <v>3229.440703122783</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3275.509442953445</v>
+        <v>3119.198573482186</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>3163.882109372654</v>
+        <v>3013.844809919833</v>
       </c>
     </row>
     <row r="13">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.078388929099871</v>
+        <v>1.079223858960387</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24441,7 +24441,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24593,13 +24593,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>3102.301102022996</v>
+        <v>2956.705412848488</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>4168.517271806365</v>
+        <v>3955.110941964158</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>2288.494407227272</v>
+        <v>2191.884467122702</v>
       </c>
     </row>
     <row r="59">
